--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/LAMPADA LED 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/LAMPADA LED 03_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LAMPADA  LED  2 LADOS 12-80V 007278</t>
+          <t xml:space="preserve"> LAMPADA   IRON  2 LADOS H4 12-80V 007278</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAMPADA LED TALLION FAROL H4</t>
+          <t>LAMPADA  TALLION FAROL H4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +472,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAMPADA LED IRON 20W 8-80V 351904</t>
+          <t>LAMPADA  IRON 20W 8-80V 351904</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +492,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAMPADA LED WURTH 12V 30/ 30W</t>
+          <t>LAMPADA  WURTH 12V 30/ 30W</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +512,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAMPADA LED WURTH 12V 55W</t>
+          <t>LAMPADA WURTH 12V 55W</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -541,7 +532,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAMPADA LED 12V 35/ 35W</t>
+          <t>LAMPADA WURTH 12V 35/ 35W</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -562,7 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAMPADA LED PHILIPS 12V 35</t>
+          <t>LAMPADA  PHILIPS 12V 35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -583,7 +572,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +584,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LAMPADA LED HALOGENA IRON BIZ100/ BIZ125 043069</t>
+          <t xml:space="preserve"> LAMPADA  HALOGENA IRON BIZ100/ BIZ125 043069</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +592,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +624,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAMPADA LED HALOGENA IRON 12V 35x35W BIZ100/ BIZ125 038663</t>
+          <t>LAMPADA  HALOGENA IRON 12V 35x35W BIZ100/ BIZ125 038663</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -659,7 +644,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAMPADA LED PHILIPS 12V 35/35W H4FITMOTOC1</t>
+          <t>LAMPADA PHILIPS 12V 35/35W H4  37791060</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -667,7 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -680,7 +664,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAMPADA LED PHILIPS 12V 35/35W  12153ESC1</t>
+          <t>LAMPADA M5 PHILIPS 12V 35/35W  35185960</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -688,7 +672,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -701,7 +684,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAMPADA LED PHILIPS S2 12V 35/35W 12728C1</t>
+          <t>LAMPADA  PHILIPS S2 12V 35/35W 12728C1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -709,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -722,7 +704,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LAMPADA LED PHILIPS 12V 4W</t>
+          <t>LAMPADA  PHILIPS 12V 4W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -730,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -751,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
